--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run2/epoch_30/per_file_predictions_epoch_30.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run2/epoch_30/per_file_predictions_epoch_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.5379,0.1066,0.0096,0.3584</t>
-  </si>
-  <si>
-    <t>0.0236,0.0033,0.0240,0.9650</t>
-  </si>
-  <si>
-    <t>0.1149,0.0078,0.0056,0.9396</t>
-  </si>
-  <si>
-    <t>0.1111,0.0332,0.0810,0.8729</t>
-  </si>
-  <si>
-    <t>0.9960,0.0004,0.0000,0.0012</t>
-  </si>
-  <si>
-    <t>0.9953,0.0012,0.0003,0.0009</t>
-  </si>
-  <si>
-    <t>0.9800,0.0161,0.0024,0.0012</t>
-  </si>
-  <si>
-    <t>0.9920,0.0015,0.0005,0.0020</t>
-  </si>
-  <si>
-    <t>0.9894,0.0050,0.0006,0.0015</t>
-  </si>
-  <si>
-    <t>0.9674,0.0254,0.0040,0.0019</t>
-  </si>
-  <si>
-    <t>0.9931,0.0017,0.0004,0.0016</t>
-  </si>
-  <si>
-    <t>0.9951,0.0006,0.0002,0.0019</t>
-  </si>
-  <si>
-    <t>0.2514,0.4384,0.4091,0.0170</t>
-  </si>
-  <si>
-    <t>0.2619,0.0100,0.8665,0.0044</t>
-  </si>
-  <si>
-    <t>0.2366,0.1968,0.5823,0.0024</t>
-  </si>
-  <si>
-    <t>0.1598,0.0455,0.7832,0.0446</t>
-  </si>
-  <si>
-    <t>0.7485,0.0417,0.2317,0.0294</t>
-  </si>
-  <si>
-    <t>0.0032,0.9933,0.0068,0.0001</t>
-  </si>
-  <si>
-    <t>0.0094,0.9898,0.0031,0.0001</t>
-  </si>
-  <si>
-    <t>0.1345,0.8698,0.0361,0.0018</t>
-  </si>
-  <si>
-    <t>0.0079,0.9868,0.0047,0.0008</t>
-  </si>
-  <si>
-    <t>0.0020,0.9951,0.0092,0.0001</t>
-  </si>
-  <si>
-    <t>0.4327,0.0412,0.3258,0.2215</t>
-  </si>
-  <si>
-    <t>0.2535,0.0968,0.6124,0.0781</t>
-  </si>
-  <si>
-    <t>0.1339,0.0380,0.8799,0.0139</t>
-  </si>
-  <si>
-    <t>0.0937,0.0327,0.7882,0.1004</t>
-  </si>
-  <si>
-    <t>0.3523,0.0482,0.6741,0.0177</t>
-  </si>
-  <si>
-    <t>0.1769,0.0249,0.8571,0.0095</t>
-  </si>
-  <si>
-    <t>0.0014,0.0014,0.9922,0.0141</t>
-  </si>
-  <si>
-    <t>0.1172,0.8700,0.0449,0.0072</t>
-  </si>
-  <si>
-    <t>0.4971,0.3071,0.1977,0.0553</t>
-  </si>
-  <si>
-    <t>0.0035,0.0377,0.9893,0.0023</t>
-  </si>
-  <si>
-    <t>0.0565,0.7781,0.3384,0.0027</t>
-  </si>
-  <si>
-    <t>0.9159,0.0355,0.0294,0.0075</t>
-  </si>
-  <si>
-    <t>0.2217,0.0288,0.8413,0.0138</t>
-  </si>
-  <si>
-    <t>0.3911,0.6910,0.0190,0.0018</t>
-  </si>
-  <si>
-    <t>0.0125,0.9488,0.2534,0.0039</t>
-  </si>
-  <si>
-    <t>0.0061,0.7597,0.9016,0.0020</t>
-  </si>
-  <si>
-    <t>0.0100,0.0519,0.9458,0.0352</t>
-  </si>
-  <si>
-    <t>0.0066,0.1800,0.9733,0.0022</t>
-  </si>
-  <si>
-    <t>0.1666,0.0144,0.5084,0.3080</t>
-  </si>
-  <si>
-    <t>0.0085,0.1083,0.9782,0.0011</t>
-  </si>
-  <si>
-    <t>0.0205,0.9080,0.2176,0.0012</t>
-  </si>
-  <si>
-    <t>0.0089,0.0886,0.9405,0.0207</t>
-  </si>
-  <si>
-    <t>0.0509,0.0758,0.0191,0.9566</t>
-  </si>
-  <si>
-    <t>0.0075,0.9775,0.0281,0.0031</t>
-  </si>
-  <si>
-    <t>0.0013,0.9920,0.0385,0.0006</t>
-  </si>
-  <si>
-    <t>0.0016,0.9869,0.0780,0.0029</t>
-  </si>
-  <si>
-    <t>0.0043,0.4751,0.9543,0.0009</t>
-  </si>
-  <si>
-    <t>0.0010,0.0168,0.9956,0.0016</t>
-  </si>
-  <si>
-    <t>0.2499,0.0115,0.8459,0.0073</t>
-  </si>
-  <si>
-    <t>0.0152,0.0061,0.9841,0.0037</t>
-  </si>
-  <si>
-    <t>0.0326,0.1044,0.9105,0.0265</t>
-  </si>
-  <si>
-    <t>0.0034,0.0097,0.9934,0.0008</t>
-  </si>
-  <si>
-    <t>0.8968,0.1433,0.0045,0.0023</t>
-  </si>
-  <si>
-    <t>0.8993,0.0736,0.0271,0.0119</t>
-  </si>
-  <si>
-    <t>0.9483,0.0127,0.0141,0.0155</t>
-  </si>
-  <si>
-    <t>0.0454,0.0396,0.9577,0.0092</t>
-  </si>
-  <si>
-    <t>0.9826,0.0045,0.0013,0.0046</t>
-  </si>
-  <si>
-    <t>0.9886,0.0042,0.0003,0.0024</t>
-  </si>
-  <si>
-    <t>0.7559,0.2303,0.0693,0.0074</t>
-  </si>
-  <si>
-    <t>0.0009,0.8520,0.9446,0.0002</t>
-  </si>
-  <si>
-    <t>0.0007,0.1246,0.9959,0.0001</t>
-  </si>
-  <si>
-    <t>0.0075,0.0387,0.9805,0.0067</t>
-  </si>
-  <si>
-    <t>0.0001,0.7540,0.9953,0.0000</t>
-  </si>
-  <si>
-    <t>0.0154,0.0145,0.9657,0.0163</t>
-  </si>
-  <si>
-    <t>0.0107,0.9705,0.0422,0.0006</t>
-  </si>
-  <si>
-    <t>0.0098,0.9846,0.0072,0.0001</t>
-  </si>
-  <si>
-    <t>0.7055,0.0122,0.3980,0.0283</t>
-  </si>
-  <si>
-    <t>0.4850,0.2813,0.3495,0.0387</t>
-  </si>
-  <si>
-    <t>0.0114,0.2937,0.9219,0.0015</t>
-  </si>
-  <si>
-    <t>0.0020,0.7624,0.9198,0.0002</t>
-  </si>
-  <si>
-    <t>0.0013,0.8989,0.8454,0.0001</t>
-  </si>
-  <si>
-    <t>0.0018,0.9227,0.8014,0.0003</t>
-  </si>
-  <si>
-    <t>0.0032,0.8804,0.8336,0.0009</t>
-  </si>
-  <si>
-    <t>0.0206,0.0065,0.0273,0.9672</t>
-  </si>
-  <si>
-    <t>0.0016,0.0030,0.0040,0.9968</t>
-  </si>
-  <si>
-    <t>0.0072,0.0120,0.0188,0.9830</t>
-  </si>
-  <si>
-    <t>0.0110,0.0068,0.0158,0.9818</t>
-  </si>
-  <si>
-    <t>0.0296,0.0081,0.0101,0.9770</t>
-  </si>
-  <si>
-    <t>0.0018,0.0234,0.0014,0.9973</t>
-  </si>
-  <si>
-    <t>0.0011,0.9328,0.8160,0.0002</t>
-  </si>
-  <si>
-    <t>0.0010,0.7520,0.9695,0.0002</t>
-  </si>
-  <si>
-    <t>0.0094,0.8113,0.7634,0.0035</t>
-  </si>
-  <si>
-    <t>0.0083,0.6450,0.8922,0.0017</t>
-  </si>
-  <si>
-    <t>0.0001,0.9697,0.9533,0.0000</t>
-  </si>
-  <si>
-    <t>0.0020,0.8694,0.8862,0.0005</t>
-  </si>
-  <si>
-    <t>0.9926,0.0014,0.0007,0.0014</t>
-  </si>
-  <si>
-    <t>0.9701,0.0221,0.0031,0.0034</t>
-  </si>
-  <si>
-    <t>0.9487,0.0397,0.0066,0.0083</t>
-  </si>
-  <si>
-    <t>0.9863,0.0066,0.0008,0.0022</t>
-  </si>
-  <si>
-    <t>0.9692,0.0103,0.0057,0.0064</t>
-  </si>
-  <si>
-    <t>0.9925,0.0015,0.0002,0.0022</t>
-  </si>
-  <si>
-    <t>0.9852,0.0038,0.0005,0.0058</t>
-  </si>
-  <si>
-    <t>0.9542,0.0350,0.0032,0.0056</t>
-  </si>
-  <si>
-    <t>0.9932,0.0004,0.0001,0.0044</t>
-  </si>
-  <si>
-    <t>0.9910,0.0030,0.0005,0.0019</t>
-  </si>
-  <si>
-    <t>0.9965,0.0003,0.0000,0.0014</t>
-  </si>
-  <si>
-    <t>0.9951,0.0004,0.0002,0.0017</t>
-  </si>
-  <si>
-    <t>0.9881,0.0010,0.0002,0.0044</t>
-  </si>
-  <si>
-    <t>0.9913,0.0020,0.0006,0.0020</t>
-  </si>
-  <si>
-    <t>0.9948,0.0007,0.0001,0.0017</t>
-  </si>
-  <si>
-    <t>0.9902,0.0013,0.0004,0.0033</t>
-  </si>
-  <si>
-    <t>0.0008,0.0026,0.9839,0.0404</t>
-  </si>
-  <si>
-    <t>0.0348,0.0594,0.9416,0.0100</t>
-  </si>
-  <si>
-    <t>0.6098,0.0061,0.1503,0.1743</t>
-  </si>
-  <si>
-    <t>0.5147,0.0121,0.6269,0.0105</t>
-  </si>
-  <si>
-    <t>0.0055,0.9902,0.0018,0.0011</t>
-  </si>
-  <si>
-    <t>0.0858,0.9250,0.0097,0.0016</t>
-  </si>
-  <si>
-    <t>0.4265,0.6559,0.0170,0.0055</t>
-  </si>
-  <si>
-    <t>0.0342,0.9615,0.0021,0.0051</t>
-  </si>
-  <si>
-    <t>0.0545,0.9464,0.0092,0.0009</t>
-  </si>
-  <si>
-    <t>0.0160,0.9846,0.0017,0.0003</t>
-  </si>
-  <si>
-    <t>0.5723,0.5820,0.0082,0.0027</t>
-  </si>
-  <si>
-    <t>0.3483,0.4043,0.3176,0.0366</t>
-  </si>
-  <si>
-    <t>0.2823,0.0074,0.8742,0.0028</t>
-  </si>
-  <si>
-    <t>0.0585,0.8689,0.1205,0.0387</t>
-  </si>
-  <si>
-    <t>0.4296,0.0423,0.6644,0.0058</t>
-  </si>
-  <si>
-    <t>0.1358,0.1793,0.1094,0.8078</t>
-  </si>
-  <si>
-    <t>0.0028,0.9840,0.0791,0.0001</t>
-  </si>
-  <si>
-    <t>0.0056,0.9773,0.0590,0.0034</t>
-  </si>
-  <si>
-    <t>0.0168,0.8994,0.0193,0.5056</t>
-  </si>
-  <si>
-    <t>0.0001,0.9865,0.8065,0.0000</t>
-  </si>
-  <si>
-    <t>0.0033,0.9884,0.0625,0.0003</t>
-  </si>
-  <si>
-    <t>0.7012,0.2959,0.0485,0.0014</t>
-  </si>
-  <si>
-    <t>0.7209,0.3333,0.0268,0.0037</t>
-  </si>
-  <si>
-    <t>0.9690,0.0102,0.0138,0.0035</t>
-  </si>
-  <si>
-    <t>0.9836,0.0032,0.0008,0.0052</t>
-  </si>
-  <si>
-    <t>0.9875,0.0005,0.0004,0.0075</t>
-  </si>
-  <si>
-    <t>0.9616,0.0041,0.0065,0.0187</t>
-  </si>
-  <si>
-    <t>0.9922,0.0009,0.0002,0.0033</t>
-  </si>
-  <si>
-    <t>0.9368,0.0226,0.0113,0.0203</t>
-  </si>
-  <si>
-    <t>0.9775,0.0010,0.0022,0.0121</t>
-  </si>
-  <si>
-    <t>0.9856,0.0011,0.0007,0.0069</t>
-  </si>
-  <si>
-    <t>0.0024,0.7470,0.9356,0.0004</t>
-  </si>
-  <si>
-    <t>0.0057,0.2270,0.9677,0.0010</t>
-  </si>
-  <si>
-    <t>0.0493,0.1584,0.8722,0.0018</t>
-  </si>
-  <si>
-    <t>0.0215,0.2173,0.9135,0.0036</t>
-  </si>
-  <si>
-    <t>0.6113,0.0789,0.2991,0.1343</t>
-  </si>
-  <si>
-    <t>0.8505,0.0514,0.0576,0.0110</t>
-  </si>
-  <si>
-    <t>0.4448,0.0057,0.7347,0.0150</t>
-  </si>
-  <si>
-    <t>0.4167,0.4679,0.1348,0.0196</t>
-  </si>
-  <si>
-    <t>0.0250,0.0573,0.0039,0.9829</t>
-  </si>
-  <si>
-    <t>0.0004,0.0016,0.0077,0.9969</t>
-  </si>
-  <si>
-    <t>0.0044,0.0148,0.0082,0.9918</t>
-  </si>
-  <si>
-    <t>0.0300,0.0083,0.0204,0.9663</t>
-  </si>
-  <si>
-    <t>0.0019,0.8431,0.6143,0.0093</t>
-  </si>
-  <si>
-    <t>0.9619,0.0197,0.0019,0.0102</t>
-  </si>
-  <si>
-    <t>0.0731,0.9123,0.0199,0.0133</t>
-  </si>
-  <si>
-    <t>0.9808,0.0025,0.0010,0.0128</t>
-  </si>
-  <si>
-    <t>0.5788,0.5092,0.0205,0.0038</t>
-  </si>
-  <si>
-    <t>0.9571,0.0134,0.0086,0.0081</t>
-  </si>
-  <si>
-    <t>0.4135,0.0215,0.0537,0.6110</t>
-  </si>
-  <si>
-    <t>0.9556,0.0060,0.0030,0.0275</t>
-  </si>
-  <si>
-    <t>0.0110,0.1912,0.9421,0.0128</t>
-  </si>
-  <si>
-    <t>0.2965,0.0089,0.0080,0.8193</t>
-  </si>
-  <si>
-    <t>0.5530,0.0370,0.0438,0.4603</t>
-  </si>
-  <si>
-    <t>0.6513,0.2031,0.1870,0.0171</t>
-  </si>
-  <si>
-    <t>0.8911,0.0378,0.0575,0.0115</t>
-  </si>
-  <si>
-    <t>0.9224,0.0248,0.0559,0.0030</t>
-  </si>
-  <si>
-    <t>0.2336,0.7210,0.0988,0.0222</t>
-  </si>
-  <si>
-    <t>0.8102,0.0959,0.0937,0.0032</t>
-  </si>
-  <si>
-    <t>0.6726,0.2433,0.0895,0.0159</t>
-  </si>
-  <si>
-    <t>0.9813,0.0042,0.0022,0.0048</t>
-  </si>
-  <si>
-    <t>0.9894,0.0024,0.0003,0.0049</t>
-  </si>
-  <si>
-    <t>0.9877,0.0039,0.0005,0.0028</t>
-  </si>
-  <si>
-    <t>0.9316,0.0216,0.0228,0.0248</t>
-  </si>
-  <si>
-    <t>0.9826,0.0061,0.0042,0.0025</t>
-  </si>
-  <si>
-    <t>0.9472,0.0411,0.0004,0.0071</t>
-  </si>
-  <si>
-    <t>0.9925,0.0007,0.0003,0.0031</t>
-  </si>
-  <si>
-    <t>0.9854,0.0040,0.0014,0.0036</t>
-  </si>
-  <si>
-    <t>0.2137,0.8067,0.0101,0.0047</t>
-  </si>
-  <si>
-    <t>0.5943,0.5171,0.0147,0.0017</t>
-  </si>
-  <si>
-    <t>0.2661,0.8384,0.0042,0.0011</t>
-  </si>
-  <si>
-    <t>0.4430,0.0703,0.6419,0.0467</t>
-  </si>
-  <si>
-    <t>0.9533,0.0365,0.0083,0.0026</t>
-  </si>
-  <si>
-    <t>0.8351,0.1555,0.0274,0.0104</t>
-  </si>
-  <si>
-    <t>0.9713,0.0106,0.0077,0.0063</t>
-  </si>
-  <si>
-    <t>0.9326,0.0259,0.0322,0.0085</t>
-  </si>
-  <si>
-    <t>0.0059,0.0486,0.9893,0.0009</t>
-  </si>
-  <si>
-    <t>0.9655,0.0210,0.0048,0.0057</t>
-  </si>
-  <si>
-    <t>0.0025,0.0217,0.9945,0.0005</t>
-  </si>
-  <si>
-    <t>0.0007,0.0714,0.9942,0.0011</t>
-  </si>
-  <si>
-    <t>0.0564,0.0140,0.9527,0.0044</t>
-  </si>
-  <si>
-    <t>0.0072,0.0939,0.9769,0.0025</t>
-  </si>
-  <si>
-    <t>0.0772,0.0996,0.8769,0.0042</t>
-  </si>
-  <si>
-    <t>0.0056,0.0053,0.9929,0.0013</t>
-  </si>
-  <si>
-    <t>0.0042,0.0182,0.9895,0.0018</t>
-  </si>
-  <si>
-    <t>0.2225,0.0510,0.7797,0.0084</t>
-  </si>
-  <si>
-    <t>0.4612,0.1420,0.4653,0.0045</t>
-  </si>
-  <si>
-    <t>0.0586,0.3757,0.7851,0.0056</t>
-  </si>
-  <si>
-    <t>0.2192,0.2464,0.5645,0.0055</t>
-  </si>
-  <si>
-    <t>0.2354,0.1445,0.6534,0.0054</t>
-  </si>
-  <si>
-    <t>0.7351,0.0291,0.3286,0.0092</t>
-  </si>
-  <si>
-    <t>0.4930,0.1127,0.4528,0.0390</t>
-  </si>
-  <si>
-    <t>0.6195,0.1056,0.2874,0.0286</t>
-  </si>
-  <si>
-    <t>0.6844,0.3717,0.0127,0.0134</t>
-  </si>
-  <si>
-    <t>0.9210,0.1088,0.0048,0.0022</t>
-  </si>
-  <si>
-    <t>0.6945,0.3514,0.0331,0.0072</t>
-  </si>
-  <si>
-    <t>0.9246,0.0802,0.0050,0.0055</t>
-  </si>
-  <si>
-    <t>0.2665,0.7579,0.0069,0.0151</t>
-  </si>
-  <si>
-    <t>0.5864,0.0687,0.4683,0.0137</t>
-  </si>
-  <si>
-    <t>0.7929,0.0233,0.1158,0.0372</t>
-  </si>
-  <si>
-    <t>0.6061,0.0706,0.1885,0.1526</t>
-  </si>
-  <si>
-    <t>0.5318,0.0284,0.3306,0.1224</t>
-  </si>
-  <si>
-    <t>0.6027,0.0228,0.0583,0.3230</t>
-  </si>
-  <si>
-    <t>0.0040,0.0168,0.9725,0.0349</t>
-  </si>
-  <si>
-    <t>0.0102,0.1576,0.9453,0.0124</t>
-  </si>
-  <si>
-    <t>0.0048,0.0465,0.9761,0.0119</t>
-  </si>
-  <si>
-    <t>0.0134,0.2134,0.9485,0.0016</t>
-  </si>
-  <si>
-    <t>0.0140,0.3741,0.8822,0.0069</t>
-  </si>
-  <si>
-    <t>0.9780,0.0073,0.0016,0.0065</t>
-  </si>
-  <si>
-    <t>0.9895,0.0035,0.0010,0.0017</t>
-  </si>
-  <si>
-    <t>0.9801,0.0076,0.0008,0.0037</t>
-  </si>
-  <si>
-    <t>0.9843,0.0055,0.0007,0.0035</t>
-  </si>
-  <si>
-    <t>0.9929,0.0014,0.0007,0.0018</t>
-  </si>
-  <si>
-    <t>0.9726,0.0163,0.0081,0.0026</t>
-  </si>
-  <si>
-    <t>0.9806,0.0014,0.0003,0.0098</t>
-  </si>
-  <si>
-    <t>0.9851,0.0052,0.0029,0.0024</t>
-  </si>
-  <si>
-    <t>0.0845,0.0271,0.9402,0.0040</t>
-  </si>
-  <si>
-    <t>0.3254,0.5517,0.1936,0.0156</t>
-  </si>
-  <si>
-    <t>0.9029,0.0362,0.0495,0.0142</t>
-  </si>
-  <si>
-    <t>0.0051,0.0130,0.9892,0.0033</t>
-  </si>
-  <si>
-    <t>0.0019,0.0114,0.9943,0.0026</t>
-  </si>
-  <si>
-    <t>0.0510,0.0908,0.9150,0.0014</t>
-  </si>
-  <si>
-    <t>0.0002,0.0036,0.9988,0.0007</t>
-  </si>
-  <si>
-    <t>0.0296,0.0165,0.9456,0.0165</t>
-  </si>
-  <si>
-    <t>0.0023,0.0201,0.9914,0.0026</t>
-  </si>
-  <si>
-    <t>0.0059,0.0668,0.9704,0.0017</t>
-  </si>
-  <si>
-    <t>0.2982,0.1209,0.6273,0.0313</t>
-  </si>
-  <si>
-    <t>0.5876,0.0110,0.4120,0.0466</t>
-  </si>
-  <si>
-    <t>0.5569,0.0247,0.4380,0.0568</t>
-  </si>
-  <si>
-    <t>0.8015,0.0120,0.2446,0.0085</t>
-  </si>
-  <si>
-    <t>0.9823,0.0054,0.0002,0.0040</t>
-  </si>
-  <si>
-    <t>0.9898,0.0019,0.0005,0.0027</t>
-  </si>
-  <si>
-    <t>0.9950,0.0017,0.0002,0.0008</t>
-  </si>
-  <si>
-    <t>0.9732,0.0150,0.0037,0.0034</t>
-  </si>
-  <si>
-    <t>0.9858,0.0035,0.0005,0.0032</t>
-  </si>
-  <si>
-    <t>0.9937,0.0021,0.0005,0.0008</t>
-  </si>
-  <si>
-    <t>0.9742,0.0211,0.0022,0.0017</t>
-  </si>
-  <si>
-    <t>0.9619,0.0135,0.0010,0.0087</t>
-  </si>
-  <si>
-    <t>0.0707,0.1493,0.8475,0.0047</t>
-  </si>
-  <si>
-    <t>0.0021,0.0322,0.9915,0.0019</t>
-  </si>
-  <si>
-    <t>0.0046,0.0461,0.9822,0.0042</t>
-  </si>
-  <si>
-    <t>0.1629,0.0532,0.7866,0.0331</t>
-  </si>
-  <si>
-    <t>0.0030,0.0076,0.9825,0.0178</t>
-  </si>
-  <si>
-    <t>0.0930,0.0028,0.6329,0.3130</t>
-  </si>
-  <si>
-    <t>0.0937,0.2350,0.6240,0.1481</t>
-  </si>
-  <si>
-    <t>0.0036,0.0274,0.9792,0.0086</t>
-  </si>
-  <si>
-    <t>0.1473,0.0023,0.0123,0.9120</t>
-  </si>
-  <si>
-    <t>0.0113,0.0178,0.0157,0.9825</t>
-  </si>
-  <si>
-    <t>0.0192,0.0417,0.0073,0.9835</t>
-  </si>
-  <si>
-    <t>0.0029,0.0018,0.0056,0.9946</t>
-  </si>
-  <si>
-    <t>0.0030,0.0019,0.0007,0.9977</t>
-  </si>
-  <si>
-    <t>0.3039,0.0415,0.0187,0.8146</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.2593,0.0201,0.0079,0.8459</t>
+  </si>
+  <si>
+    <t>0.0036,0.0125,0.0014,0.9965</t>
+  </si>
+  <si>
+    <t>0.2403,0.0064,0.0157,0.8354</t>
+  </si>
+  <si>
+    <t>0.1200,0.0277,0.0137,0.9301</t>
+  </si>
+  <si>
+    <t>0.9976,0.0001,0.0000,0.0010</t>
+  </si>
+  <si>
+    <t>0.9929,0.0008,0.0001,0.0024</t>
+  </si>
+  <si>
+    <t>0.9843,0.0039,0.0026,0.0031</t>
+  </si>
+  <si>
+    <t>0.9922,0.0016,0.0003,0.0019</t>
+  </si>
+  <si>
+    <t>0.9650,0.0212,0.0090,0.0037</t>
+  </si>
+  <si>
+    <t>0.9868,0.0086,0.0013,0.0013</t>
+  </si>
+  <si>
+    <t>0.9951,0.0002,0.0000,0.0026</t>
+  </si>
+  <si>
+    <t>0.9954,0.0002,0.0000,0.0023</t>
+  </si>
+  <si>
+    <t>0.6623,0.0984,0.2940,0.0149</t>
+  </si>
+  <si>
+    <t>0.4385,0.0478,0.5032,0.0849</t>
+  </si>
+  <si>
+    <t>0.1979,0.0591,0.8371,0.0013</t>
+  </si>
+  <si>
+    <t>0.3052,0.3659,0.4097,0.0211</t>
+  </si>
+  <si>
+    <t>0.9185,0.0152,0.0683,0.0045</t>
+  </si>
+  <si>
+    <t>0.0027,0.9917,0.0270,0.0002</t>
+  </si>
+  <si>
+    <t>0.0017,0.9952,0.0062,0.0005</t>
+  </si>
+  <si>
+    <t>0.2757,0.7543,0.0176,0.0050</t>
+  </si>
+  <si>
+    <t>0.0034,0.9935,0.0047,0.0004</t>
+  </si>
+  <si>
+    <t>0.0012,0.9967,0.0076,0.0001</t>
+  </si>
+  <si>
+    <t>0.4281,0.0236,0.5933,0.0318</t>
+  </si>
+  <si>
+    <t>0.5543,0.0263,0.4139,0.0540</t>
+  </si>
+  <si>
+    <t>0.0514,0.0140,0.9628,0.0029</t>
+  </si>
+  <si>
+    <t>0.3197,0.0071,0.7807,0.0148</t>
+  </si>
+  <si>
+    <t>0.0506,0.0043,0.9473,0.0228</t>
+  </si>
+  <si>
+    <t>0.2180,0.0089,0.8351,0.0133</t>
+  </si>
+  <si>
+    <t>0.0009,0.0057,0.9946,0.0057</t>
+  </si>
+  <si>
+    <t>0.5629,0.4413,0.0498,0.0125</t>
+  </si>
+  <si>
+    <t>0.6930,0.1531,0.1919,0.0065</t>
+  </si>
+  <si>
+    <t>0.0032,0.0121,0.9946,0.0020</t>
+  </si>
+  <si>
+    <t>0.0046,0.9587,0.2494,0.0003</t>
+  </si>
+  <si>
+    <t>0.8726,0.0927,0.0189,0.0123</t>
+  </si>
+  <si>
+    <t>0.8672,0.0803,0.0407,0.0172</t>
+  </si>
+  <si>
+    <t>0.1913,0.8562,0.0063,0.0082</t>
+  </si>
+  <si>
+    <t>0.0150,0.9380,0.3589,0.0044</t>
+  </si>
+  <si>
+    <t>0.0392,0.4503,0.7234,0.0154</t>
+  </si>
+  <si>
+    <t>0.0125,0.0777,0.9477,0.0142</t>
+  </si>
+  <si>
+    <t>0.0103,0.2551,0.9462,0.0030</t>
+  </si>
+  <si>
+    <t>0.0497,0.0189,0.9053,0.0634</t>
+  </si>
+  <si>
+    <t>0.0063,0.1024,0.9693,0.0081</t>
+  </si>
+  <si>
+    <t>0.0355,0.8582,0.2654,0.0035</t>
+  </si>
+  <si>
+    <t>0.0390,0.0871,0.9207,0.0149</t>
+  </si>
+  <si>
+    <t>0.1607,0.5653,0.0846,0.7312</t>
+  </si>
+  <si>
+    <t>0.0018,0.9891,0.0215,0.0088</t>
+  </si>
+  <si>
+    <t>0.0026,0.9844,0.1245,0.0005</t>
+  </si>
+  <si>
+    <t>0.0010,0.9903,0.0325,0.0071</t>
+  </si>
+  <si>
+    <t>0.0137,0.4186,0.8924,0.0040</t>
+  </si>
+  <si>
+    <t>0.0012,0.0752,0.9939,0.0004</t>
+  </si>
+  <si>
+    <t>0.0699,0.0135,0.9430,0.0076</t>
+  </si>
+  <si>
+    <t>0.2033,0.0029,0.9156,0.0029</t>
+  </si>
+  <si>
+    <t>0.0035,0.0906,0.9785,0.0043</t>
+  </si>
+  <si>
+    <t>0.0142,0.1026,0.9546,0.0016</t>
+  </si>
+  <si>
+    <t>0.8919,0.1328,0.0085,0.0038</t>
+  </si>
+  <si>
+    <t>0.9768,0.0042,0.0103,0.0040</t>
+  </si>
+  <si>
+    <t>0.9484,0.0156,0.0039,0.0196</t>
+  </si>
+  <si>
+    <t>0.0275,0.0972,0.9495,0.0164</t>
+  </si>
+  <si>
+    <t>0.9870,0.0039,0.0010,0.0036</t>
+  </si>
+  <si>
+    <t>0.9646,0.0347,0.0024,0.0025</t>
+  </si>
+  <si>
+    <t>0.9731,0.0124,0.0022,0.0067</t>
+  </si>
+  <si>
+    <t>0.0007,0.8409,0.9596,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.0573,0.9913,0.0012</t>
+  </si>
+  <si>
+    <t>0.0018,0.0227,0.9914,0.0025</t>
+  </si>
+  <si>
+    <t>0.0019,0.6186,0.9706,0.0005</t>
+  </si>
+  <si>
+    <t>0.0044,0.0036,0.9916,0.0035</t>
+  </si>
+  <si>
+    <t>0.0248,0.9380,0.0753,0.0006</t>
+  </si>
+  <si>
+    <t>0.0083,0.9870,0.0017,0.0006</t>
+  </si>
+  <si>
+    <t>0.8199,0.0784,0.1025,0.0129</t>
+  </si>
+  <si>
+    <t>0.8640,0.0799,0.0564,0.0029</t>
+  </si>
+  <si>
+    <t>0.0075,0.0436,0.9865,0.0017</t>
+  </si>
+  <si>
+    <t>0.0015,0.8810,0.8780,0.0002</t>
+  </si>
+  <si>
+    <t>0.0026,0.7490,0.9092,0.0002</t>
+  </si>
+  <si>
+    <t>0.0017,0.9774,0.2137,0.0002</t>
+  </si>
+  <si>
+    <t>0.0016,0.7169,0.9522,0.0003</t>
+  </si>
+  <si>
+    <t>0.0118,0.0039,0.0817,0.9510</t>
+  </si>
+  <si>
+    <t>0.0042,0.0062,0.0035,0.9951</t>
+  </si>
+  <si>
+    <t>0.0020,0.2259,0.0139,0.9844</t>
+  </si>
+  <si>
+    <t>0.0666,0.0068,0.0084,0.9618</t>
+  </si>
+  <si>
+    <t>0.0205,0.0079,0.0122,0.9797</t>
+  </si>
+  <si>
+    <t>0.0009,0.0038,0.0044,0.9973</t>
+  </si>
+  <si>
+    <t>0.0010,0.8672,0.9251,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.7720,0.9811,0.0000</t>
+  </si>
+  <si>
+    <t>0.0172,0.6056,0.8289,0.0032</t>
+  </si>
+  <si>
+    <t>0.0030,0.5748,0.9537,0.0005</t>
+  </si>
+  <si>
+    <t>0.0008,0.8376,0.9435,0.0001</t>
+  </si>
+  <si>
+    <t>0.0089,0.4062,0.9369,0.0020</t>
+  </si>
+  <si>
+    <t>0.9832,0.0015,0.0005,0.0071</t>
+  </si>
+  <si>
+    <t>0.9714,0.0187,0.0006,0.0022</t>
+  </si>
+  <si>
+    <t>0.9488,0.0237,0.0012,0.0123</t>
+  </si>
+  <si>
+    <t>0.9674,0.0215,0.0036,0.0035</t>
+  </si>
+  <si>
+    <t>0.9915,0.0041,0.0003,0.0012</t>
+  </si>
+  <si>
+    <t>0.9884,0.0027,0.0004,0.0026</t>
+  </si>
+  <si>
+    <t>0.9745,0.0206,0.0022,0.0026</t>
+  </si>
+  <si>
+    <t>0.9809,0.0045,0.0007,0.0061</t>
+  </si>
+  <si>
+    <t>0.9944,0.0007,0.0002,0.0020</t>
+  </si>
+  <si>
+    <t>0.9951,0.0017,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9896,0.0009,0.0002,0.0051</t>
+  </si>
+  <si>
+    <t>0.9937,0.0009,0.0005,0.0016</t>
+  </si>
+  <si>
+    <t>0.9844,0.0052,0.0026,0.0030</t>
+  </si>
+  <si>
+    <t>0.9887,0.0018,0.0007,0.0042</t>
+  </si>
+  <si>
+    <t>0.9850,0.0029,0.0020,0.0030</t>
+  </si>
+  <si>
+    <t>0.9948,0.0013,0.0005,0.0009</t>
+  </si>
+  <si>
+    <t>0.0016,0.0014,0.9940,0.0063</t>
+  </si>
+  <si>
+    <t>0.0678,0.0175,0.8985,0.0464</t>
+  </si>
+  <si>
+    <t>0.4823,0.0068,0.3782,0.1369</t>
+  </si>
+  <si>
+    <t>0.2180,0.0053,0.7643,0.0470</t>
+  </si>
+  <si>
+    <t>0.0342,0.9666,0.0072,0.0004</t>
+  </si>
+  <si>
+    <t>0.0200,0.9805,0.0030,0.0005</t>
+  </si>
+  <si>
+    <t>0.0350,0.9514,0.0276,0.0024</t>
+  </si>
+  <si>
+    <t>0.0675,0.9296,0.0150,0.0027</t>
+  </si>
+  <si>
+    <t>0.1543,0.8857,0.0065,0.0018</t>
+  </si>
+  <si>
+    <t>0.0085,0.9874,0.0024,0.0005</t>
+  </si>
+  <si>
+    <t>0.3686,0.7117,0.0045,0.0097</t>
+  </si>
+  <si>
+    <t>0.5268,0.2563,0.2346,0.0149</t>
+  </si>
+  <si>
+    <t>0.6151,0.0268,0.4479,0.0188</t>
+  </si>
+  <si>
+    <t>0.3017,0.3857,0.3810,0.0425</t>
+  </si>
+  <si>
+    <t>0.5202,0.1741,0.3364,0.0474</t>
+  </si>
+  <si>
+    <t>0.4341,0.0676,0.2521,0.3330</t>
+  </si>
+  <si>
+    <t>0.0029,0.9873,0.0532,0.0004</t>
+  </si>
+  <si>
+    <t>0.0021,0.9850,0.0106,0.0276</t>
+  </si>
+  <si>
+    <t>0.0022,0.9761,0.0083,0.3323</t>
+  </si>
+  <si>
+    <t>0.0004,0.9836,0.6426,0.0001</t>
+  </si>
+  <si>
+    <t>0.0120,0.9766,0.0393,0.0004</t>
+  </si>
+  <si>
+    <t>0.7229,0.2971,0.0310,0.0014</t>
+  </si>
+  <si>
+    <t>0.6888,0.2632,0.0876,0.0032</t>
+  </si>
+  <si>
+    <t>0.9647,0.0225,0.0061,0.0021</t>
+  </si>
+  <si>
+    <t>0.9770,0.0048,0.0021,0.0090</t>
+  </si>
+  <si>
+    <t>0.9904,0.0009,0.0004,0.0035</t>
+  </si>
+  <si>
+    <t>0.9782,0.0048,0.0065,0.0041</t>
+  </si>
+  <si>
+    <t>0.9858,0.0014,0.0003,0.0064</t>
+  </si>
+  <si>
+    <t>0.8269,0.1449,0.0452,0.0264</t>
+  </si>
+  <si>
+    <t>0.9670,0.0123,0.0074,0.0063</t>
+  </si>
+  <si>
+    <t>0.9830,0.0048,0.0023,0.0036</t>
+  </si>
+  <si>
+    <t>0.0029,0.5292,0.9500,0.0009</t>
+  </si>
+  <si>
+    <t>0.0055,0.4042,0.9583,0.0007</t>
+  </si>
+  <si>
+    <t>0.0082,0.2227,0.9564,0.0010</t>
+  </si>
+  <si>
+    <t>0.0179,0.0242,0.9814,0.0008</t>
+  </si>
+  <si>
+    <t>0.7912,0.0707,0.1113,0.0495</t>
+  </si>
+  <si>
+    <t>0.6536,0.0619,0.3791,0.0076</t>
+  </si>
+  <si>
+    <t>0.3905,0.0057,0.7946,0.0095</t>
+  </si>
+  <si>
+    <t>0.4832,0.0447,0.4226,0.1143</t>
+  </si>
+  <si>
+    <t>0.0664,0.0026,0.0065,0.9643</t>
+  </si>
+  <si>
+    <t>0.0004,0.0011,0.0081,0.9962</t>
+  </si>
+  <si>
+    <t>0.0033,0.0042,0.0045,0.9947</t>
+  </si>
+  <si>
+    <t>0.0194,0.0078,0.0050,0.9869</t>
+  </si>
+  <si>
+    <t>0.0031,0.8257,0.8817,0.0022</t>
+  </si>
+  <si>
+    <t>0.9441,0.0113,0.0029,0.0287</t>
+  </si>
+  <si>
+    <t>0.3841,0.6252,0.0493,0.0144</t>
+  </si>
+  <si>
+    <t>0.9435,0.0028,0.0031,0.0448</t>
+  </si>
+  <si>
+    <t>0.5761,0.5332,0.0079,0.0073</t>
+  </si>
+  <si>
+    <t>0.9479,0.0050,0.0054,0.0275</t>
+  </si>
+  <si>
+    <t>0.1323,0.0197,0.0130,0.9269</t>
+  </si>
+  <si>
+    <t>0.9761,0.0083,0.0066,0.0036</t>
+  </si>
+  <si>
+    <t>0.0075,0.2449,0.9110,0.0310</t>
+  </si>
+  <si>
+    <t>0.7740,0.0123,0.0775,0.1420</t>
+  </si>
+  <si>
+    <t>0.8944,0.0050,0.0028,0.0815</t>
+  </si>
+  <si>
+    <t>0.3237,0.6999,0.0190,0.0095</t>
+  </si>
+  <si>
+    <t>0.7303,0.2676,0.0312,0.0193</t>
+  </si>
+  <si>
+    <t>0.8929,0.0412,0.0589,0.0062</t>
+  </si>
+  <si>
+    <t>0.3280,0.5295,0.0665,0.0935</t>
+  </si>
+  <si>
+    <t>0.6212,0.2709,0.1195,0.0098</t>
+  </si>
+  <si>
+    <t>0.8071,0.0673,0.1370,0.0048</t>
+  </si>
+  <si>
+    <t>0.9881,0.0033,0.0029,0.0019</t>
+  </si>
+  <si>
+    <t>0.9883,0.0032,0.0012,0.0031</t>
+  </si>
+  <si>
+    <t>0.9877,0.0045,0.0039,0.0011</t>
+  </si>
+  <si>
+    <t>0.9842,0.0005,0.0002,0.0132</t>
+  </si>
+  <si>
+    <t>0.9768,0.0026,0.0022,0.0096</t>
+  </si>
+  <si>
+    <t>0.9918,0.0021,0.0005,0.0024</t>
+  </si>
+  <si>
+    <t>0.9899,0.0013,0.0003,0.0039</t>
+  </si>
+  <si>
+    <t>0.9861,0.0033,0.0009,0.0041</t>
+  </si>
+  <si>
+    <t>0.3055,0.6995,0.0454,0.0046</t>
+  </si>
+  <si>
+    <t>0.7028,0.4078,0.0168,0.0043</t>
+  </si>
+  <si>
+    <t>0.6123,0.5223,0.0075,0.0043</t>
+  </si>
+  <si>
+    <t>0.8705,0.0490,0.0606,0.0229</t>
+  </si>
+  <si>
+    <t>0.8417,0.2028,0.0083,0.0047</t>
+  </si>
+  <si>
+    <t>0.9320,0.0435,0.0207,0.0039</t>
+  </si>
+  <si>
+    <t>0.9394,0.0745,0.0042,0.0026</t>
+  </si>
+  <si>
+    <t>0.7975,0.1766,0.0582,0.0108</t>
+  </si>
+  <si>
+    <t>0.0399,0.0309,0.9663,0.0048</t>
+  </si>
+  <si>
+    <t>0.9692,0.0140,0.0107,0.0017</t>
+  </si>
+  <si>
+    <t>0.0054,0.0228,0.9870,0.0027</t>
+  </si>
+  <si>
+    <t>0.0279,0.1413,0.9157,0.0152</t>
+  </si>
+  <si>
+    <t>0.0115,0.0063,0.9909,0.0013</t>
+  </si>
+  <si>
+    <t>0.0009,0.1639,0.9913,0.0002</t>
+  </si>
+  <si>
+    <t>0.0152,0.0111,0.9831,0.0020</t>
+  </si>
+  <si>
+    <t>0.0106,0.0028,0.9920,0.0010</t>
+  </si>
+  <si>
+    <t>0.0539,0.0278,0.9421,0.0027</t>
+  </si>
+  <si>
+    <t>0.4003,0.0837,0.5303,0.0703</t>
+  </si>
+  <si>
+    <t>0.1502,0.1503,0.7725,0.0116</t>
+  </si>
+  <si>
+    <t>0.2780,0.1836,0.5919,0.0104</t>
+  </si>
+  <si>
+    <t>0.2259,0.1135,0.7093,0.0058</t>
+  </si>
+  <si>
+    <t>0.3690,0.0954,0.6256,0.0155</t>
+  </si>
+  <si>
+    <t>0.5571,0.0788,0.4605,0.0088</t>
+  </si>
+  <si>
+    <t>0.5629,0.2202,0.2592,0.0442</t>
+  </si>
+  <si>
+    <t>0.5345,0.1401,0.3683,0.0376</t>
+  </si>
+  <si>
+    <t>0.8856,0.1307,0.0162,0.0050</t>
+  </si>
+  <si>
+    <t>0.0818,0.9220,0.0152,0.0026</t>
+  </si>
+  <si>
+    <t>0.9621,0.0217,0.0056,0.0052</t>
+  </si>
+  <si>
+    <t>0.9696,0.0198,0.0014,0.0036</t>
+  </si>
+  <si>
+    <t>0.6712,0.4370,0.0042,0.0108</t>
+  </si>
+  <si>
+    <t>0.5442,0.0867,0.4680,0.0121</t>
+  </si>
+  <si>
+    <t>0.7393,0.0316,0.2764,0.0142</t>
+  </si>
+  <si>
+    <t>0.4137,0.2517,0.3624,0.0124</t>
+  </si>
+  <si>
+    <t>0.5570,0.0409,0.4724,0.0429</t>
+  </si>
+  <si>
+    <t>0.8014,0.0136,0.1336,0.0282</t>
+  </si>
+  <si>
+    <t>0.0197,0.0324,0.9366,0.0412</t>
+  </si>
+  <si>
+    <t>0.0293,0.0615,0.9493,0.0074</t>
+  </si>
+  <si>
+    <t>0.0199,0.0140,0.9595,0.0248</t>
+  </si>
+  <si>
+    <t>0.0664,0.0105,0.9539,0.0046</t>
+  </si>
+  <si>
+    <t>0.0187,0.0584,0.9195,0.0328</t>
+  </si>
+  <si>
+    <t>0.9850,0.0021,0.0002,0.0057</t>
+  </si>
+  <si>
+    <t>0.9658,0.0333,0.0044,0.0020</t>
+  </si>
+  <si>
+    <t>0.9882,0.0037,0.0003,0.0022</t>
+  </si>
+  <si>
+    <t>0.9869,0.0061,0.0017,0.0013</t>
+  </si>
+  <si>
+    <t>0.9857,0.0060,0.0011,0.0025</t>
+  </si>
+  <si>
+    <t>0.9869,0.0121,0.0008,0.0012</t>
+  </si>
+  <si>
+    <t>0.9893,0.0024,0.0007,0.0026</t>
+  </si>
+  <si>
+    <t>0.9728,0.0071,0.0055,0.0062</t>
+  </si>
+  <si>
+    <t>0.3805,0.0085,0.8474,0.0036</t>
+  </si>
+  <si>
+    <t>0.3868,0.2697,0.4764,0.0178</t>
+  </si>
+  <si>
+    <t>0.8221,0.0389,0.0371,0.0788</t>
+  </si>
+  <si>
+    <t>0.0023,0.0030,0.9954,0.0018</t>
+  </si>
+  <si>
+    <t>0.0008,0.0088,0.9972,0.0011</t>
+  </si>
+  <si>
+    <t>0.0323,0.0894,0.8720,0.0489</t>
+  </si>
+  <si>
+    <t>0.0003,0.0034,0.9973,0.0027</t>
+  </si>
+  <si>
+    <t>0.1697,0.0315,0.8089,0.0419</t>
+  </si>
+  <si>
+    <t>0.0005,0.0028,0.9972,0.0026</t>
+  </si>
+  <si>
+    <t>0.0074,0.0193,0.9815,0.0034</t>
+  </si>
+  <si>
+    <t>0.2204,0.2218,0.6197,0.0193</t>
+  </si>
+  <si>
+    <t>0.6843,0.0260,0.4103,0.0081</t>
+  </si>
+  <si>
+    <t>0.5962,0.0171,0.4369,0.0513</t>
+  </si>
+  <si>
+    <t>0.7022,0.0068,0.2003,0.0605</t>
+  </si>
+  <si>
+    <t>0.9686,0.0072,0.0011,0.0120</t>
+  </si>
+  <si>
+    <t>0.9907,0.0036,0.0007,0.0014</t>
+  </si>
+  <si>
+    <t>0.9919,0.0035,0.0009,0.0009</t>
+  </si>
+  <si>
+    <t>0.9825,0.0053,0.0009,0.0055</t>
+  </si>
+  <si>
+    <t>0.9845,0.0071,0.0006,0.0025</t>
+  </si>
+  <si>
+    <t>0.9710,0.0229,0.0051,0.0020</t>
+  </si>
+  <si>
+    <t>0.9739,0.0150,0.0048,0.0033</t>
+  </si>
+  <si>
+    <t>0.9814,0.0060,0.0011,0.0042</t>
+  </si>
+  <si>
+    <t>0.0288,0.2796,0.8353,0.0069</t>
+  </si>
+  <si>
+    <t>0.0019,0.0393,0.9930,0.0009</t>
+  </si>
+  <si>
+    <t>0.0042,0.0226,0.9879,0.0031</t>
+  </si>
+  <si>
+    <t>0.0811,0.0813,0.8357,0.0107</t>
+  </si>
+  <si>
+    <t>0.0029,0.0048,0.9782,0.0346</t>
+  </si>
+  <si>
+    <t>0.3938,0.0055,0.6411,0.0441</t>
+  </si>
+  <si>
+    <t>0.1452,0.0047,0.9038,0.0122</t>
+  </si>
+  <si>
+    <t>0.0102,0.0335,0.8543,0.1745</t>
+  </si>
+  <si>
+    <t>0.5100,0.0007,0.0182,0.5033</t>
+  </si>
+  <si>
+    <t>0.0047,0.0273,0.0206,0.9847</t>
+  </si>
+  <si>
+    <t>0.0715,0.0060,0.0155,0.9511</t>
+  </si>
+  <si>
+    <t>0.0055,0.0044,0.0130,0.9892</t>
+  </si>
+  <si>
+    <t>0.0067,0.0021,0.0051,0.9915</t>
+  </si>
+  <si>
+    <t>0.3255,0.0283,0.0155,0.7551</t>
   </si>
 </sst>
 </file>
@@ -1956,10 +1965,10 @@
         <v>259</v>
       </c>
       <c r="C2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,7 +1996,7 @@
         <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2136,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2150,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2164,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,10 +2175,10 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2192,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2234,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,10 +2273,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,10 +2287,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,10 +2371,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2379,7 +2388,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2416,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,10 +2441,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2449,7 +2458,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,10 +2483,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2528,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2542,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2581,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2640,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2654,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2920,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2925,7 +2934,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2948,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2962,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2976,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,10 +2987,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +3004,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3102,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3116,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,7 +3130,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,7 +3144,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3158,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,10 +3169,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,10 +3435,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3508,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3541,7 +3550,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3564,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,10 +3575,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,10 +3589,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,10 +3603,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,10 +3617,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,10 +3659,10 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3676,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3704,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,7 +3718,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,7 +3844,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3849,7 +3858,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3872,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3914,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3928,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,10 +3939,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4012,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4031,7 +4040,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,10 +4065,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,7 +4096,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,10 +4135,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,10 +4163,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4199,7 +4208,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4353,7 +4362,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,10 +4373,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,10 +4387,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,10 +4401,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4600,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,10 +4611,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4619,7 +4628,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4633,7 +4642,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4647,7 +4656,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4661,7 +4670,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,7 +4684,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4689,7 +4698,7 @@
         <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4712,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,10 +4723,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4740,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,10 +4765,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,7 +4782,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,10 +4807,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4815,7 +4824,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4838,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4866,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4908,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5045,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5174,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5188,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,7 +5202,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5403,7 +5412,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5440,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,10 +5451,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5515,7 +5524,7 @@
         <v>260</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
